--- a/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
+++ b/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,11 @@
           <t>nameKey</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>cooldown</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -459,6 +464,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -479,6 +489,11 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>名称文本键(fg.TbLocText)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>核心固件发动后的冷却秒数(FGR-SIG-033:冷却属于信号,跳到别的机器不重置;按游戏时间计,暂停不走);只在 kind=core 时生效,常规固件填 0</t>
         </is>
       </c>
     </row>
@@ -499,6 +514,9 @@
           <t>firmware.fw_homing.name</t>
         </is>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -517,6 +535,9 @@
           <t>firmware.fw_split.name</t>
         </is>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -535,6 +556,9 @@
           <t>firmware.fw_trail.name</t>
         </is>
       </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -553,6 +577,9 @@
           <t>firmware.fw_overload.name</t>
         </is>
       </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -571,6 +598,9 @@
           <t>firmware.fw_marktag.name</t>
         </is>
       </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -588,6 +618,9 @@
         <is>
           <t>firmware.fw_armorpierce.name</t>
         </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
+++ b/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,7 +569,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>core</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>core</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -621,6 +621,90 @@
       </c>
       <c r="E9" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fw_capacitor</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>firmware.fw_capacitor.name</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fw_swarm</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>firmware.fw_swarm.name</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fw_amplify</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>firmware.fw_amplify.name</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fw_execute</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>firmware.fw_execute.name</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
+++ b/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,16 @@
           <t>cooldown</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>protocol</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>faction</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -469,6 +479,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -494,6 +514,16 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>核心固件发动后的冷却秒数(FGR-SIG-033:冷却属于信号,跳到别的机器不重置;按游戏时间计,暂停不走);只在 kind=core 时生效,常规固件填 0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>协议:own=己方/中立(无需破解),enemy=敌方加密(解析台破解前只能放进信号核裸跑,不能装进机器电路或炮塔)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>来源阵营:reclaim=归还,silent=静默,foundry=铸造;暴露面板“各阵营贡献”与异派技术判定读这里,名称走文本键 faction.&lt;值&gt;</t>
         </is>
       </c>
     </row>
@@ -517,6 +547,16 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -538,6 +578,16 @@
       <c r="E5" t="n">
         <v>0</v>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -559,6 +609,16 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -580,6 +640,16 @@
       <c r="E7" t="n">
         <v>8</v>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -601,6 +671,16 @@
       <c r="E8" t="n">
         <v>8</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -622,6 +702,16 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -643,6 +733,16 @@
       <c r="E10" t="n">
         <v>8</v>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -664,6 +764,16 @@
       <c r="E11" t="n">
         <v>8</v>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -685,6 +795,16 @@
       <c r="E12" t="n">
         <v>8</v>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -705,6 +825,16 @@
       </c>
       <c r="E13" t="n">
         <v>8</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
+++ b/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>faction</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +494,11 @@
           <t>string</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -524,6 +534,11 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>来源阵营:reclaim=归还,silent=静默,foundry=铸造;暴露面板“各阵营贡献”与异派技术判定读这里,名称走文本键 faction.&lt;值&gt;</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>类别:fuse=引信与弹芯,limiter=限制器与击发逻辑,fluid=流体改道,em=电磁场控;机身形变按类别切换(引信类不改机身),核心固件必须是 limiter(设计案 5.3)</t>
         </is>
       </c>
     </row>
@@ -557,6 +572,11 @@
           <t>reclaim</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -588,6 +608,11 @@
           <t>reclaim</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -619,6 +644,11 @@
           <t>reclaim</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -650,6 +680,11 @@
           <t>reclaim</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -681,6 +716,11 @@
           <t>silent</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -712,6 +752,11 @@
           <t>foundry</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -743,6 +788,11 @@
           <t>reclaim</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -774,6 +824,11 @@
           <t>reclaim</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -805,6 +860,11 @@
           <t>reclaim</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -834,6 +894,11 @@
       <c r="G13" t="inlineStr">
         <is>
           <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>limiter</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
+++ b/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:Z47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,96 @@
           <t>category</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>legacyId</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>descKey</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>rarity</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>heat</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>readProjectileKey</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>readMeleeKey</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>readSummonKey</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>readAuraKey</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>readFieldKey</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>morph</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>acquireKey</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>cracked</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>scrap</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -499,6 +589,96 @@
           <t>string</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -539,6 +719,96 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>类别:fuse=引信与弹芯,limiter=限制器与击发逻辑,fluid=流体改道,em=电磁场控;机身形变按类别切换(引信类不改机身),核心固件必须是 limiter(设计案 5.3)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>旧基因ID(gene_*,仅追溯与调试层;设计案 5.4“新建”的两条填 none)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>描述文本键</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>稀有度:common=普通,rare=稀有,epic=精良(文本键 firmware.rarity.&lt;值&gt;)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>负载(装进机器电路时占用底盘负载;接入口插入不占,FGR-SIG-023)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>能耗:每发耗电(机器电池;FG2-FW-01 起进双态预览与蓝图版本,战斗内耗电见 DEBT-FG2FW01-02)</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>热量:每发积热(热量预算与重炮内核积热都读它;熔穿过载时过载这一项由反应的 +25 取代)</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>读法文本键:装在射弹上</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>读法文本键:装在格斗上</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>读法文本键:装在无人机上</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>读法文本键:装在力场上</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>读法文本键:装在布区上</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>产生的状态标签(fg.TbStatusTag 的ID,分号分隔;none=不产生)</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>机身形变状态:none=常态(引信类只改弹体特效),limiter=形变态,fluid=喷口态,em=线圈态(文本键 morph.state.&lt;值&gt;,须与类别对应)</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>图标ID(GameRes/Raw/UI/Icons/&lt;icon&gt;.png;芯片外形 + 类别角标,tools/icons/gen_placeholder_icons.py)</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>获取途径:base=基础蓝图库,terminal=遗迹终端数据盒,cache=技术缓存,relic=人类遗产,salvage=杂兵残骸,elite=精英三选一,boss=阵营首领</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>获取途径说明文本键(图鉴与锁定提示)</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>出厂即已破解(己方/中立=True;敌方加密=False,解析台破解后才能装进机器,FGR-SIG-060)</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>装进蓝图的废料成本(蓝图版本成本;刻印芯片的废料另见 signal.firmware_chip.print_scrap)</t>
         </is>
       </c>
     </row>
@@ -577,12 +847,94 @@
           <t>fuse</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>gene_taxis</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>firmware.fw_homing.desc</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>firmware.fw_homing.read.projectile</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>firmware.fw_homing.read.melee</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>firmware.fw_homing.read.summon</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>firmware.fw_homing.read.aura</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>firmware.fw_homing.read.field</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>icon_fw_homing</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>firmware.acquire.base</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fw_split</t>
+          <t>fw_lockcache</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -592,7 +944,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>firmware.fw_split.name</t>
+          <t>firmware.fw_lockcache.name</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -600,25 +952,107 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>reclaim</t>
+          <t>relic</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>fuse</t>
         </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>gene_receptor</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>firmware.fw_lockcache.desc</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>firmware.fw_lockcache.read.projectile</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>firmware.fw_lockcache.read.melee</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>firmware.fw_lockcache.read.summon</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>firmware.fw_lockcache.read.aura</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>firmware.fw_lockcache.read.field</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>ReceptorMemory</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>icon_fw_lockcache</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>relic</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>firmware.acquire.relic</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fw_trail</t>
+          <t>fw_scatter</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -628,7 +1062,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>firmware.fw_trail.name</t>
+          <t>firmware.fw_scatter.name</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -636,97 +1070,343 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>enemy</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>reclaim</t>
+          <t>foundry</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>fluid</t>
-        </is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>gene_spindle</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>firmware.fw_scatter.desc</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>firmware.fw_scatter.read.projectile</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>firmware.fw_scatter.read.melee</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>firmware.fw_scatter.read.summon</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>firmware.fw_scatter.read.aura</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>firmware.fw_scatter.read.field</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>icon_fw_scatter</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.foundry</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fw_overload</t>
+          <t>fw_fork</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>firmware.fw_overload.name</t>
+          <t>firmware.fw_fork.name</t>
         </is>
       </c>
       <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>gene_golgi</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>firmware.fw_fork.desc</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>firmware.fw_fork.read.projectile</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>firmware.fw_fork.read.melee</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>firmware.fw_fork.read.summon</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>firmware.fw_fork.read.aura</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>firmware.fw_fork.read.field</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>icon_fw_fork</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.foundry</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
         <v>8</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>own</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>reclaim</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>limiter</t>
-        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fw_marktag</t>
+          <t>fw_split</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>firmware.fw_marktag.name</t>
+          <t>firmware.fw_split.name</t>
         </is>
       </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>gene_split</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>firmware.fw_split.desc</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>firmware.fw_split.read.projectile</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>firmware.fw_split.read.melee</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>firmware.fw_split.read.summon</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>firmware.fw_split.read.aura</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>firmware.fw_split.read.field</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>icon_fw_split</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>firmware.acquire.base</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
         <v>8</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>enemy</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>silent</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>limiter</t>
-        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fw_armorpierce</t>
+          <t>fw_delayfuse</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -736,7 +1416,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>firmware.fw_armorpierce.name</t>
+          <t>firmware.fw_delayfuse.name</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -756,150 +1436,4572 @@
         <is>
           <t>fuse</t>
         </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>gene_bloomlate</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>firmware.fw_delayfuse.desc</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>firmware.fw_delayfuse.read.projectile</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>firmware.fw_delayfuse.read.melee</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>firmware.fw_delayfuse.read.summon</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>firmware.fw_delayfuse.read.aura</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>firmware.fw_delayfuse.read.field</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>icon_fw_delayfuse</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.foundry</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fw_capacitor</t>
+          <t>fw_cluster</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>firmware.fw_capacitor.name</t>
+          <t>firmware.fw_cluster.name</t>
         </is>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>gene_scatterseed</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>firmware.fw_cluster.desc</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>firmware.fw_cluster.read.projectile</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>firmware.fw_cluster.read.melee</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>firmware.fw_cluster.read.summon</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>firmware.fw_cluster.read.aura</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>firmware.fw_cluster.read.field</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Poison</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>icon_fw_cluster</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.foundry</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
         <v>8</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>own</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>reclaim</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>limiter</t>
-        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fw_swarm</t>
+          <t>fw_pierce</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>firmware.fw_swarm.name</t>
+          <t>firmware.fw_pierce.name</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>reclaim</t>
+          <t>relic</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>limiter</t>
-        </is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>gene_tubule</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>firmware.fw_pierce.desc</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>firmware.fw_pierce.read.projectile</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>firmware.fw_pierce.read.melee</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>firmware.fw_pierce.read.summon</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>firmware.fw_pierce.read.aura</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>firmware.fw_pierce.read.field</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>icon_fw_pierce</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>relic</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>firmware.acquire.relic</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fw_amplify</t>
+          <t>fw_corrode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>firmware.fw_amplify.name</t>
+          <t>firmware.fw_corrode.name</t>
         </is>
       </c>
       <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>gene_lyso</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>firmware.fw_corrode.desc</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>firmware.fw_corrode.read.projectile</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>firmware.fw_corrode.read.melee</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>firmware.fw_corrode.read.summon</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>firmware.fw_corrode.read.aura</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>firmware.fw_corrode.read.field</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Acid</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>icon_fw_corrode</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.foundry</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z12" t="n">
         <v>8</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>own</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>reclaim</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>limiter</t>
-        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
+          <t>fw_echo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>firmware.fw_echo.name</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>gene_echo</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>firmware.fw_echo.desc</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>firmware.fw_echo.read.projectile</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>firmware.fw_echo.read.melee</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>firmware.fw_echo.read.summon</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>firmware.fw_echo.read.aura</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>firmware.fw_echo.read.field</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>icon_fw_echo</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.foundry</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fw_arc</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>firmware.fw_arc.name</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>gene_arc</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>firmware.fw_arc.desc</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>firmware.fw_arc.read.projectile</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>firmware.fw_arc.read.melee</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>firmware.fw_arc.read.summon</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>firmware.fw_arc.read.aura</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>firmware.fw_arc.read.field</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Earth</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>icon_fw_arc</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.foundry</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fw_flare</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>firmware.fw_flare.name</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>gene_swell</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>firmware.fw_flare.desc</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>firmware.fw_flare.read.projectile</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>firmware.fw_flare.read.melee</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>firmware.fw_flare.read.summon</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>firmware.fw_flare.read.aura</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>firmware.fw_flare.read.field</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>icon_fw_flare</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.foundry</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fw_wide</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>firmware.fw_wide.name</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>gene_fan</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>firmware.fw_wide.desc</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>firmware.fw_wide.read.projectile</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>firmware.fw_wide.read.melee</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>firmware.fw_wide.read.summon</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>firmware.fw_wide.read.aura</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>firmware.fw_wide.read.field</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>icon_fw_wide</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.foundry</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>fw_jitter</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>firmware.fw_jitter.name</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>gene_drift</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>firmware.fw_jitter.desc</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>firmware.fw_jitter.read.projectile</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>firmware.fw_jitter.read.melee</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>firmware.fw_jitter.read.summon</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>firmware.fw_jitter.read.aura</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>firmware.fw_jitter.read.field</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Drifting;Haste</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>icon_fw_jitter</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>salvage</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>firmware.acquire.salvage.foundry</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>fw_ricochet</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>firmware.fw_ricochet.name</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>gene_elastic</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>firmware.fw_ricochet.desc</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>firmware.fw_ricochet.read.projectile</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>firmware.fw_ricochet.read.melee</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>firmware.fw_ricochet.read.summon</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>firmware.fw_ricochet.read.aura</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>firmware.fw_ricochet.read.field</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>icon_fw_ricochet</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>salvage</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>firmware.acquire.salvage.foundry</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z18" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>fw_wallslam</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>firmware.fw_wallslam.name</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>gene_membrane</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>firmware.fw_wallslam.desc</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>firmware.fw_wallslam.read.projectile</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>firmware.fw_wallslam.read.melee</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>firmware.fw_wallslam.read.summon</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>firmware.fw_wallslam.read.aura</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>firmware.fw_wallslam.read.field</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>WallImpact</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>icon_fw_wallslam</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.foundry</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>fw_armorpierce</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>firmware.fw_armorpierce.name</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>firmware.fw_armorpierce.desc</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>firmware.fw_armorpierce.read.projectile</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>firmware.fw_armorpierce.read.melee</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>firmware.fw_armorpierce.read.summon</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>firmware.fw_armorpierce.read.aura</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>firmware.fw_armorpierce.read.field</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>icon_fw_armorpierce</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>cache</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>firmware.acquire.cache.foundry</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>fw_overload</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>firmware.fw_overload.name</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>8</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>gene_heatshock</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>firmware.fw_overload.desc</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>15</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>firmware.fw_overload.read.projectile</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>firmware.fw_overload.read.melee</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>firmware.fw_overload.read.summon</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>firmware.fw_overload.read.aura</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>firmware.fw_overload.read.field</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>icon_fw_overload</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>firmware.acquire.base</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>fw_capacitor</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>firmware.fw_capacitor.name</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>8</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>foundry</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>gene_vacuole</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>firmware.fw_capacitor.desc</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N22" t="n">
+        <v>10</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>firmware.fw_capacitor.read.projectile</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>firmware.fw_capacitor.read.melee</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>firmware.fw_capacitor.read.summon</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>firmware.fw_capacitor.read.aura</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>firmware.fw_capacitor.read.field</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Charged</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>icon_fw_capacitor</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>firmware.acquire.boss.foundry</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>fw_marktag</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>firmware.fw_marktag.name</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>firmware.fw_marktag.desc</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>firmware.fw_marktag.read.projectile</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>firmware.fw_marktag.read.melee</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>firmware.fw_marktag.read.summon</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>firmware.fw_marktag.read.aura</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>firmware.fw_marktag.read.field</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>icon_fw_marktag</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>terminal</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>firmware.acquire.terminal.silent</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z23" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>fw_swarm</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>firmware.fw_swarm.name</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>gene_swarm</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>firmware.fw_swarm.desc</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>firmware.fw_swarm.read.projectile</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>firmware.fw_swarm.read.melee</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>firmware.fw_swarm.read.summon</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>firmware.fw_swarm.read.aura</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>firmware.fw_swarm.read.field</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>InheritPattern</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>icon_fw_swarm</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>firmware.acquire.boss.silent</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z24" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>fw_amplify</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>firmware.fw_amplify.name</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>gene_catalyst</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>firmware.fw_amplify.desc</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" t="n">
+        <v>5</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>firmware.fw_amplify.read.projectile</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>firmware.fw_amplify.read.melee</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>firmware.fw_amplify.read.summon</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>firmware.fw_amplify.read.aura</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>firmware.fw_amplify.read.field</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>icon_fw_amplify</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>firmware.acquire.boss.clarity</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z25" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>fw_execute</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>firmware.fw_execute.name</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E26" t="n">
         <v>8</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>overclock</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>gene_apoptosis</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>firmware.fw_execute.desc</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" t="n">
+        <v>5</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>firmware.fw_execute.read.projectile</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>firmware.fw_execute.read.melee</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>firmware.fw_execute.read.summon</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>firmware.fw_execute.read.aura</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>firmware.fw_execute.read.field</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Apoptosis;Dark</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>icon_fw_execute</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>firmware.acquire.boss.overclock</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z26" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>fw_clock</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>firmware.fw_clock.name</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>overclock</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>gene_rhythm</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>firmware.fw_clock.desc</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>firmware.fw_clock.read.projectile</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>firmware.fw_clock.read.melee</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>firmware.fw_clock.read.summon</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>firmware.fw_clock.read.aura</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>firmware.fw_clock.read.field</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Blood</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>icon_fw_clock</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>salvage</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>firmware.acquire.salvage.overclock</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z27" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>fw_resonance</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>firmware.fw_resonance.name</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>overclock</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>gene_harmonic</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>firmware.fw_resonance.desc</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>5</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>firmware.fw_resonance.read.projectile</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>firmware.fw_resonance.read.melee</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>firmware.fw_resonance.read.summon</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>firmware.fw_resonance.read.aura</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>firmware.fw_resonance.read.field</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>icon_fw_resonance</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.overclock</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>fw_followup</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>firmware.fw_followup.name</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>overclock</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>gene_synapse</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>firmware.fw_followup.desc</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>8</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>firmware.fw_followup.read.projectile</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>firmware.fw_followup.read.melee</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>firmware.fw_followup.read.summon</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>firmware.fw_followup.read.aura</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>firmware.fw_followup.read.field</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Shock</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>icon_fw_followup</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.overclock</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z29" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>fw_reclaim</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>firmware.fw_reclaim.name</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>overclock</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>gene_blood</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>firmware.fw_reclaim.desc</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>firmware.fw_reclaim.read.projectile</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>firmware.fw_reclaim.read.melee</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>firmware.fw_reclaim.read.summon</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>firmware.fw_reclaim.read.aura</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>firmware.fw_reclaim.read.field</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Blood</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>icon_fw_reclaim</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.overclock</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z30" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>fw_coolant</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>firmware.fw_coolant.name</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>relic</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>gene_tide</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>firmware.fw_coolant.desc</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>firmware.fw_coolant.read.projectile</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>firmware.fw_coolant.read.melee</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>firmware.fw_coolant.read.summon</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>firmware.fw_coolant.read.aura</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>firmware.fw_coolant.read.field</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Wet</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>icon_fw_coolant</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>relic</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>firmware.acquire.relic</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z31" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>fw_oilleak</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>firmware.fw_oilleak.name</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>gene_oilfilm</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>firmware.fw_oilleak.desc</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>firmware.fw_oilleak.read.projectile</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>firmware.fw_oilleak.read.melee</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>firmware.fw_oilleak.read.summon</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>firmware.fw_oilleak.read.aura</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>firmware.fw_oilleak.read.field</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Oil</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>icon_fw_oilleak</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>salvage</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>firmware.acquire.salvage.clarity</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z32" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>fw_nitrogen</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>firmware.fw_nitrogen.name</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>gene_frostfilm</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>firmware.fw_nitrogen.desc</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>6</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>firmware.fw_nitrogen.read.projectile</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>firmware.fw_nitrogen.read.melee</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>firmware.fw_nitrogen.read.summon</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>firmware.fw_nitrogen.read.aura</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>firmware.fw_nitrogen.read.field</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Frozen</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>icon_fw_nitrogen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.clarity</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z33" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>fw_acid</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>firmware.fw_acid.name</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>gene_acidfilm</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>firmware.fw_acid.desc</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>firmware.fw_acid.read.projectile</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>firmware.fw_acid.read.melee</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>firmware.fw_acid.read.summon</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>firmware.fw_acid.read.aura</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>firmware.fw_acid.read.field</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Acid</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>icon_fw_acid</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.clarity</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z34" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>fw_adhesive</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>firmware.fw_adhesive.name</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>gene_sugarfilm</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>firmware.fw_adhesive.desc</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>firmware.fw_adhesive.read.projectile</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>firmware.fw_adhesive.read.melee</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>firmware.fw_adhesive.read.summon</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>firmware.fw_adhesive.read.aura</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>firmware.fw_adhesive.read.field</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>SugarFilm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>icon_fw_adhesive</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>salvage</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>firmware.acquire.salvage.clarity</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z35" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>fw_burntrail</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>firmware.fw_burntrail.name</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>gene_pyro</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>firmware.fw_burntrail.desc</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>5</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>firmware.fw_burntrail.read.projectile</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>firmware.fw_burntrail.read.melee</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>firmware.fw_burntrail.read.summon</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>firmware.fw_burntrail.read.aura</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>firmware.fw_burntrail.read.field</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>icon_fw_burntrail</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>salvage</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>firmware.acquire.salvage.clarity</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z36" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>fw_trail</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>firmware.fw_trail.name</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>own</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>reclaim</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>limiter</t>
-        </is>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>gene_slime</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>firmware.fw_trail.desc</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>firmware.fw_trail.read.projectile</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>firmware.fw_trail.read.melee</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>firmware.fw_trail.read.summon</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>firmware.fw_trail.read.aura</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>firmware.fw_trail.read.field</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Slow</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>icon_fw_trail</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>firmware.acquire.base</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z37" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>fw_spread</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>firmware.fw_spread.name</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>gene_capillary</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>firmware.fw_spread.desc</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>firmware.fw_spread.read.projectile</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>firmware.fw_spread.read.melee</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>firmware.fw_spread.read.summon</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>firmware.fw_spread.read.aura</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>firmware.fw_spread.read.field</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Capillary;Wet</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>icon_fw_spread</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.clarity</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z38" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>fw_bridge</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>firmware.fw_bridge.name</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>clarity</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>gene_weave</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>firmware.fw_bridge.desc</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>firmware.fw_bridge.read.projectile</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>firmware.fw_bridge.read.melee</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>firmware.fw_bridge.read.summon</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>firmware.fw_bridge.read.aura</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>firmware.fw_bridge.read.field</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>icon_fw_bridge</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.clarity</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z39" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>fw_tractor</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>firmware.fw_tractor.name</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>gene_pull</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>firmware.fw_tractor.desc</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>2</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>firmware.fw_tractor.read.projectile</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>firmware.fw_tractor.read.melee</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>firmware.fw_tractor.read.summon</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>firmware.fw_tractor.read.aura</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>firmware.fw_tractor.read.field</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Earth</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>icon_fw_tractor</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.silent</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z40" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>fw_magnet</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>firmware.fw_magnet.name</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>gene_magnet</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>firmware.fw_magnet.desc</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>2</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>firmware.fw_magnet.read.projectile</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>firmware.fw_magnet.read.melee</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>firmware.fw_magnet.read.summon</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>firmware.fw_magnet.read.aura</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>firmware.fw_magnet.read.field</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Charged;Magnet</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>icon_fw_magnet</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.silent</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z41" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>fw_vortex</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>firmware.fw_vortex.name</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>gene_vortex</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>firmware.fw_vortex.desc</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>firmware.fw_vortex.read.projectile</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>firmware.fw_vortex.read.melee</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>firmware.fw_vortex.read.summon</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>firmware.fw_vortex.read.aura</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>firmware.fw_vortex.read.field</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>icon_fw_vortex</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>salvage</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>firmware.acquire.salvage.silent</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>fw_arcchain</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>firmware.fw_arcchain.name</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>gene_volt</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>firmware.fw_arcchain.desc</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>firmware.fw_arcchain.read.projectile</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>firmware.fw_arcchain.read.melee</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>firmware.fw_arcchain.read.summon</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>firmware.fw_arcchain.read.aura</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>firmware.fw_arcchain.read.field</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Shock</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>icon_fw_arcchain</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>salvage</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>firmware.acquire.salvage.silent</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>fw_boomerang</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>firmware.fw_boomerang.name</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>relic</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>gene_return</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>firmware.fw_boomerang.desc</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>firmware.fw_boomerang.read.projectile</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>firmware.fw_boomerang.read.melee</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>firmware.fw_boomerang.read.summon</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>firmware.fw_boomerang.read.aura</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>firmware.fw_boomerang.read.field</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>icon_fw_boomerang</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>relic</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>firmware.acquire.relic</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>fw_orbit</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>firmware.fw_orbit.name</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>gene_flagella</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>firmware.fw_orbit.desc</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>firmware.fw_orbit.read.projectile</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>firmware.fw_orbit.read.melee</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>firmware.fw_orbit.read.summon</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>firmware.fw_orbit.read.aura</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>firmware.fw_orbit.read.field</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>icon_fw_orbit</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.silent</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z45" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>fw_deflect</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>firmware.fw_deflect.name</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>gene_mirror</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>firmware.fw_deflect.desc</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>2</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>firmware.fw_deflect.read.projectile</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>firmware.fw_deflect.read.melee</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>firmware.fw_deflect.read.summon</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>firmware.fw_deflect.read.aura</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>firmware.fw_deflect.read.field</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Light;Mirror</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>icon_fw_deflect</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>elite</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>firmware.acquire.elite.silent</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z46" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>fw_shockwave</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>firmware.fw_shockwave.name</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>enemy</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>silent</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>gene_ripple</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>firmware.fw_shockwave.desc</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>firmware.fw_shockwave.read.projectile</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>firmware.fw_shockwave.read.melee</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>firmware.fw_shockwave.read.summon</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>firmware.fw_shockwave.read.aura</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>firmware.fw_shockwave.read.field</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Wet</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>icon_fw_shockwave</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>salvage</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>firmware.acquire.salvage.silent</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="Z47" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
+++ b/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z47"/>
+  <dimension ref="A1:AA47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,6 +547,11 @@
           <t>scrap</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>readFields</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -679,6 +684,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -809,6 +819,11 @@
       <c r="Z3" t="inlineStr">
         <is>
           <t>装进蓝图的废料成本(蓝图版本成本;刻印芯片的废料另见 signal.firmware_chip.print_scrap)</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>读法字段(FG2-FW-02):字段:幅度;…,字段见 fgdata_reading.READING_FIELDS;内核按 载体 × 字段 查 fg.TbCarrierReading</t>
         </is>
       </c>
     </row>
@@ -929,6 +944,11 @@
       <c r="Z4" t="n">
         <v>5</v>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>homing:0.85</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -1047,6 +1067,11 @@
       <c r="Z5" t="n">
         <v>5</v>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>homing:0.5</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1165,6 +1190,11 @@
       <c r="Z6" t="n">
         <v>8</v>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>count:1;spread:30</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -1283,6 +1313,11 @@
       <c r="Z7" t="n">
         <v>8</v>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>split:2</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -1401,6 +1436,11 @@
       <c r="Z8" t="n">
         <v>8</v>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>split:3</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -1519,6 +1559,11 @@
       <c r="Z9" t="n">
         <v>8</v>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>echo:0.6;split:3</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -1637,6 +1682,11 @@
       <c r="Z10" t="n">
         <v>8</v>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>explode:1;linger:2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -1755,6 +1805,11 @@
       <c r="Z11" t="n">
         <v>5</v>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>pierce:1</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -1873,6 +1928,11 @@
       <c r="Z12" t="n">
         <v>8</v>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>explode:1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -1991,6 +2051,11 @@
       <c r="Z13" t="n">
         <v>8</v>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>echo:0.4</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -2109,6 +2174,11 @@
       <c r="Z14" t="n">
         <v>12</v>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>lob:4</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -2227,6 +2297,11 @@
       <c r="Z15" t="n">
         <v>8</v>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>scale:1.5</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -2345,6 +2420,11 @@
       <c r="Z16" t="n">
         <v>8</v>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>spread:60</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -2463,6 +2543,11 @@
       <c r="Z17" t="n">
         <v>5</v>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>spread:20;tick:3</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -2581,6 +2666,11 @@
       <c r="Z18" t="n">
         <v>5</v>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>bounce:1</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -2699,6 +2789,11 @@
       <c r="Z19" t="n">
         <v>8</v>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>bounce:2</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -2817,6 +2912,11 @@
       <c r="Z20" t="n">
         <v>10</v>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>armor:0.5</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -2935,6 +3035,11 @@
       <c r="Z21" t="n">
         <v>10</v>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>heatburst:1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -3053,6 +3158,11 @@
       <c r="Z22" t="n">
         <v>12</v>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>capacitor:1.6;scale:1.3</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -3171,6 +3281,11 @@
       <c r="Z23" t="n">
         <v>12</v>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>markjump:1</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -3289,6 +3404,11 @@
       <c r="Z24" t="n">
         <v>12</v>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>inherit:1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -3407,6 +3527,11 @@
       <c r="Z25" t="n">
         <v>12</v>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>amp:0.5</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -3525,6 +3650,11 @@
       <c r="Z26" t="n">
         <v>12</v>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>explode:1</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -3643,6 +3773,11 @@
       <c r="Z27" t="n">
         <v>5</v>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>rhythm:2</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -3761,6 +3896,11 @@
       <c r="Z28" t="n">
         <v>8</v>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>echo:0.4;count:2</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -3879,6 +4019,11 @@
       <c r="Z29" t="n">
         <v>12</v>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>feedback:0.2</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -3997,6 +4142,11 @@
       <c r="Z30" t="n">
         <v>12</v>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>return:1</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -4115,6 +4265,11 @@
       <c r="Z31" t="n">
         <v>5</v>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>linger:3</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -4233,6 +4388,11 @@
       <c r="Z32" t="n">
         <v>5</v>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>linger:3</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -4351,6 +4511,11 @@
       <c r="Z33" t="n">
         <v>8</v>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>linger:3</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -4469,6 +4634,11 @@
       <c r="Z34" t="n">
         <v>8</v>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>linger:3</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
@@ -4587,6 +4757,11 @@
       <c r="Z35" t="n">
         <v>5</v>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>linger:3</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
@@ -4705,6 +4880,11 @@
       <c r="Z36" t="n">
         <v>5</v>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>trail:2</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -4823,6 +5003,11 @@
       <c r="Z37" t="n">
         <v>5</v>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>trail:1</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -4941,6 +5126,11 @@
       <c r="Z38" t="n">
         <v>12</v>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>linger:3;scale:1.2</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
@@ -5059,6 +5249,11 @@
       <c r="Z39" t="n">
         <v>12</v>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>weave:2</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
@@ -5177,6 +5372,11 @@
       <c r="Z40" t="n">
         <v>8</v>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>pull:0.5</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
@@ -5295,6 +5495,11 @@
       <c r="Z41" t="n">
         <v>12</v>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>pull:0.3</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
@@ -5413,6 +5618,11 @@
       <c r="Z42" t="n">
         <v>5</v>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>pull:0.6;orbit:90</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -5531,6 +5741,11 @@
       <c r="Z43" t="n">
         <v>5</v>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>chain:2</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
@@ -5649,6 +5864,11 @@
       <c r="Z44" t="n">
         <v>5</v>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>return:1</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
@@ -5767,6 +5987,11 @@
       <c r="Z45" t="n">
         <v>8</v>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>orbit:120</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
@@ -5885,6 +6110,11 @@
       <c r="Z46" t="n">
         <v>12</v>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>bounce:2</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -6002,6 +6232,11 @@
       </c>
       <c r="Z47" t="n">
         <v>5</v>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>grow:1</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
+++ b/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
@@ -753,12 +753,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>能耗:每发耗电(机器电池;FG2-FW-01 起进双态预览与蓝图版本,战斗内耗电见 DEBT-FG2FW01-02)</t>
+          <t>能耗:数据层保留(蓝图版本照记;FG4-ECO-04 起不产生战斗效果、界面不显示,DEBT-FG2FW01-02)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>热量:每发积热(热量预算与重炮内核积热都读它;熔穿过载时过载这一项由反应的 +25 取代)</t>
+          <t>热量:每发积热(热量预算与重炮内核积热都读它;熔穿过载时过载这一项由反应的 +25 取代;原本只有耗电的固件按 1 电=1 热折算,FG4-ECO-04)</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -884,7 +884,7 @@
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -2237,7 +2237,7 @@
         <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
         <v>2</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>2</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>2</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         <v>2</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>3</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         <v>2</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>

--- a/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
+++ b/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA47"/>
+  <dimension ref="A1:AD77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,6 +552,21 @@
           <t>readFields</t>
         </is>
       </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>mixA</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>mixB</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>category2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -689,6 +704,21 @@
           <t>string</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -824,6 +854,21 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>读法字段(FG2-FW-02):字段:幅度;…,字段见 fgdata_reading.READING_FIELDS;内核按 载体 × 字段 查 fg.TbCarrierReading</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>混合固件的父固件A(fg.TbFusionRecipe;正式固件填 none)</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>混合固件的父固件B(正式固件填 none)</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>混合固件的第二个类别(类别显示两个图标,FGR-FW-050;正式固件填 none)</t>
         </is>
       </c>
     </row>
@@ -949,6 +994,21 @@
           <t>homing:0.85</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -1072,6 +1132,21 @@
           <t>homing:0.5</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1195,6 +1270,21 @@
           <t>count:1;spread:30</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -1318,6 +1408,21 @@
           <t>split:2</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -1441,6 +1546,21 @@
           <t>split:3</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -1564,6 +1684,21 @@
           <t>echo:0.6;split:3</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -1687,6 +1822,21 @@
           <t>explode:1;linger:2</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -1810,6 +1960,21 @@
           <t>pierce:1</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -1933,6 +2098,21 @@
           <t>explode:1</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -2056,6 +2236,21 @@
           <t>echo:0.4</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -2179,6 +2374,21 @@
           <t>lob:4</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -2302,6 +2512,21 @@
           <t>scale:1.5</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -2425,6 +2650,21 @@
           <t>spread:60</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -2548,6 +2788,21 @@
           <t>spread:20;tick:3</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -2671,6 +2926,21 @@
           <t>bounce:1</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -2794,6 +3064,21 @@
           <t>bounce:2</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -2917,6 +3202,21 @@
           <t>armor:0.5</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -3040,6 +3340,21 @@
           <t>heatburst:1</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -3163,6 +3478,21 @@
           <t>capacitor:1.6;scale:1.3</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -3286,6 +3616,21 @@
           <t>markjump:1</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -3409,6 +3754,21 @@
           <t>inherit:1</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -3532,6 +3892,21 @@
           <t>amp:0.5</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -3655,6 +4030,21 @@
           <t>explode:1</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -3778,6 +4168,21 @@
           <t>rhythm:2</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -3901,6 +4306,21 @@
           <t>echo:0.4;count:2</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -4024,6 +4444,21 @@
           <t>feedback:0.2</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -4147,6 +4582,21 @@
           <t>return:1</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -4270,6 +4720,21 @@
           <t>linger:3</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -4393,6 +4858,21 @@
           <t>linger:3</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -4516,6 +4996,21 @@
           <t>linger:3</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -4639,6 +5134,21 @@
           <t>linger:3</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
@@ -4762,6 +5272,21 @@
           <t>linger:3</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
@@ -4885,6 +5410,21 @@
           <t>trail:2</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -5008,6 +5548,21 @@
           <t>trail:1</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -5131,6 +5686,21 @@
           <t>linger:3;scale:1.2</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
@@ -5254,6 +5824,21 @@
           <t>weave:2</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
@@ -5377,6 +5962,21 @@
           <t>pull:0.5</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
@@ -5500,6 +6100,21 @@
           <t>pull:0.3</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
@@ -5623,6 +6238,21 @@
           <t>pull:0.6;orbit:90</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -5746,6 +6376,21 @@
           <t>chain:2</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
@@ -5869,6 +6514,21 @@
           <t>return:1</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
@@ -5992,6 +6652,21 @@
           <t>orbit:120</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
@@ -6115,6 +6790,21 @@
           <t>bounce:2</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -6236,6 +6926,4161 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>grow:1</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>fw_mix_napalm</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>fusion.napalm.name</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_napalm.desc</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>2</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>7</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_napalm.read.projectile</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_napalm.read.melee</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_napalm.read.summon</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_napalm.read.aura</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_napalm.read.field</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Fire;Oil</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_napalm</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z48" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>trail:2;linger:3</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>fw_burntrail</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>fw_oilleak</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>fw_mix_flashover</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>fusion.flashover.name</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>8</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_flashover.desc</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>2</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>17</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_flashover.read.projectile</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_flashover.read.melee</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_flashover.read.summon</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_flashover.read.aura</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_flashover.read.field</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Fire;Oil</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_flashover</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z49" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>heatburst:1;linger:3</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>fw_overload</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>fw_oilleak</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>fw_mix_steamjet</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>fusion.steamjet.name</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_steamjet.desc</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>2</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>9</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_steamjet.read.projectile</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_steamjet.read.melee</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_steamjet.read.summon</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_steamjet.read.aura</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_steamjet.read.field</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Fire;Wet</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_steamjet</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z50" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>trail:2;linger:3</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>fw_burntrail</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>fw_coolant</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>fw_mix_cryoflame</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>fusion.cryoflame.name</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_cryoflame.desc</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>2</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>11</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_cryoflame.read.projectile</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_cryoflame.read.melee</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_cryoflame.read.summon</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_cryoflame.read.aura</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_cryoflame.read.field</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Fire;Frozen</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_cryoflame</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z51" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>trail:2;linger:3</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>fw_burntrail</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>fw_nitrogen</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>fw_mix_thermalspike</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>fusion.thermalspike.name</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>8</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_thermalspike.desc</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>2</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>21</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_thermalspike.read.projectile</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_thermalspike.read.melee</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_thermalspike.read.summon</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_thermalspike.read.aura</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_thermalspike.read.field</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Fire;Frozen</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_thermalspike</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z52" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>heatburst:1;linger:3</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>fw_overload</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>fw_nitrogen</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>fw_mix_causticflame</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>fusion.causticflame.name</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_causticflame.desc</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2</v>
+      </c>
+      <c r="N53" t="n">
+        <v>7</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_causticflame.read.projectile</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_causticflame.read.melee</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_causticflame.read.summon</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_causticflame.read.aura</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_causticflame.read.field</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Fire;Acid</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_causticflame</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z53" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>trail:2;linger:3</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>fw_burntrail</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>fw_acid</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>fw_mix_causticshell</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>fusion.causticshell.name</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_causticshell.desc</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>2</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" t="n">
+        <v>6</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_causticshell.read.projectile</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_causticshell.read.melee</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_causticshell.read.summon</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_causticshell.read.aura</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_causticshell.read.field</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Acid;Fire</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_causticshell</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z54" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>explode:1;trail:2</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>fw_corrode</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>fw_burntrail</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>fw_mix_glassburst</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>fusion.glassburst.name</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_glassburst.desc</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>3</v>
+      </c>
+      <c r="M55" t="n">
+        <v>2</v>
+      </c>
+      <c r="N55" t="n">
+        <v>7</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_glassburst.read.projectile</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_glassburst.read.melee</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_glassburst.read.summon</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_glassburst.read.aura</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_glassburst.read.field</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Earth;Fire</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_glassburst</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z55" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>lob:4;trail:2</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>fw_arc</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>fw_burntrail</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>fw_mix_cinderpull</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>fusion.cinderpull.name</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_cinderpull.desc</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>2</v>
+      </c>
+      <c r="M56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N56" t="n">
+        <v>7</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_cinderpull.read.projectile</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_cinderpull.read.melee</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_cinderpull.read.summon</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_cinderpull.read.aura</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_cinderpull.read.field</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Earth;Fire</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_cinderpull</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z56" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>pull:0.5;trail:2</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>fw_tractor</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>fw_burntrail</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>fw_mix_wetarc</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>fusion.wetarc.name</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_wetarc.desc</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>2</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3</v>
+      </c>
+      <c r="N57" t="n">
+        <v>7</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_wetarc.read.projectile</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_wetarc.read.melee</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_wetarc.read.summon</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_wetarc.read.aura</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_wetarc.read.field</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Shock;Wet</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_wetarc</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>chain:2;linger:3</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>fw_arcchain</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>fw_coolant</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>fw_mix_stormwave</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>fusion.stormwave.name</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_stormwave.desc</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>2</v>
+      </c>
+      <c r="M58" t="n">
+        <v>5</v>
+      </c>
+      <c r="N58" t="n">
+        <v>5</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_stormwave.read.projectile</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_stormwave.read.melee</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_stormwave.read.summon</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_stormwave.read.aura</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_stormwave.read.field</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Wet;Shock</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_stormwave</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z58" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>grow:1;chain:2</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>fw_shockwave</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>fw_arcchain</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>fw_mix_shortloop</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>fusion.shortloop.name</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_shortloop.desc</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>3</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" t="n">
+        <v>12</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_shortloop.read.projectile</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_shortloop.read.melee</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_shortloop.read.summon</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_shortloop.read.aura</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_shortloop.read.field</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Shock;Wet</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_shortloop</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z59" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>feedback:0.2;linger:3</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>fw_followup</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>fw_coolant</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>fw_mix_electrolyte</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>fusion.electrolyte.name</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_electrolyte.desc</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>2</v>
+      </c>
+      <c r="M60" t="n">
+        <v>5</v>
+      </c>
+      <c r="N60" t="n">
+        <v>5</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_electrolyte.read.projectile</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_electrolyte.read.melee</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_electrolyte.read.summon</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_electrolyte.read.aura</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_electrolyte.read.field</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Shock;Acid</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_electrolyte</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z60" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>chain:2;linger:3</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>fw_arcchain</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>fw_acid</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>fw_mix_ioncorrode</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>fusion.ioncorrode.name</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_ioncorrode.desc</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>3</v>
+      </c>
+      <c r="M61" t="n">
+        <v>2</v>
+      </c>
+      <c r="N61" t="n">
+        <v>9</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_ioncorrode.read.projectile</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_ioncorrode.read.melee</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_ioncorrode.read.summon</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_ioncorrode.read.aura</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_ioncorrode.read.field</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Shock;Acid</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_ioncorrode</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z61" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>feedback:0.2;explode:1</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>fw_followup</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>fw_corrode</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>fw_mix_insulfoam</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>fusion.insulfoam.name</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_insulfoam.desc</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>2</v>
+      </c>
+      <c r="M62" t="n">
+        <v>3</v>
+      </c>
+      <c r="N62" t="n">
+        <v>5</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_insulfoam.read.projectile</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_insulfoam.read.melee</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_insulfoam.read.summon</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_insulfoam.read.aura</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_insulfoam.read.field</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Shock;Oil</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_insulfoam</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z62" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>chain:2;linger:3</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>fw_arcchain</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>fw_oilleak</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>fw_mix_gumacid</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>fusion.gumacid.name</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_gumacid.desc</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>2</v>
+      </c>
+      <c r="M63" t="n">
+        <v>2</v>
+      </c>
+      <c r="N63" t="n">
+        <v>4</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_gumacid.read.projectile</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_gumacid.read.melee</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_gumacid.read.summon</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_gumacid.read.aura</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_gumacid.read.field</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Acid;SugarFilm</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_gumacid</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z63" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>linger:4.5</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>fw_acid</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>fw_adhesive</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>fw_mix_stickyshell</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>fusion.stickyshell.name</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_stickyshell.desc</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>2</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_stickyshell.read.projectile</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_stickyshell.read.melee</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_stickyshell.read.summon</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_stickyshell.read.aura</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_stickyshell.read.field</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Acid;SugarFilm</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_stickyshell</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z64" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>explode:1;linger:3</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>fw_corrode</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>fw_adhesive</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>fw_mix_rustclock</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>fusion.rustclock.name</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustclock.desc</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>2</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3</v>
+      </c>
+      <c r="N65" t="n">
+        <v>7</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustclock.read.projectile</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustclock.read.melee</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustclock.read.summon</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustclock.read.aura</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustclock.read.field</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Blood;Acid</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_rustclock</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z65" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>rhythm:2;linger:3</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>fw_clock</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>fw_acid</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>fw_mix_meltreclaim</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>fusion.meltreclaim.name</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_meltreclaim.desc</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>3</v>
+      </c>
+      <c r="M66" t="n">
+        <v>2</v>
+      </c>
+      <c r="N66" t="n">
+        <v>2</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_meltreclaim.read.projectile</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_meltreclaim.read.melee</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_meltreclaim.read.summon</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_meltreclaim.read.aura</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_meltreclaim.read.field</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Blood;Acid</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_meltreclaim</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z66" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>return:1;explode:1</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>fw_reclaim</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>fw_corrode</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>fw_mix_bindflow</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>fusion.bindflow.name</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_bindflow.desc</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>2</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>6</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_bindflow.read.projectile</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_bindflow.read.melee</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_bindflow.read.summon</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_bindflow.read.aura</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_bindflow.read.field</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Wet;SugarFilm</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_bindflow</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z67" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>linger:4.5</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>fw_coolant</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>fw_adhesive</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>fw_mix_bindspread</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>fusion.bindspread.name</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_bindspread.desc</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>3</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>5</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_bindspread.read.projectile</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_bindspread.read.melee</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_bindspread.read.summon</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_bindspread.read.aura</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_bindspread.read.field</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Capillary;Wet;SugarFilm</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_bindspread</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z68" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>linger:4.5;scale:1.2</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>fw_spread</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>fw_adhesive</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>fw_mix_etchslick</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>fusion.etchslick.name</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchslick.desc</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>2</v>
+      </c>
+      <c r="M69" t="n">
+        <v>2</v>
+      </c>
+      <c r="N69" t="n">
+        <v>4</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchslick.read.projectile</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchslick.read.melee</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchslick.read.summon</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchslick.read.aura</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchslick.read.field</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Acid;Oil</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_etchslick</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z69" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>linger:4.5</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>fw_acid</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>fw_oilleak</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>fw_mix_etchshell</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>fusion.etchshell.name</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchshell.desc</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>2</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" t="n">
+        <v>3</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchshell.read.projectile</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchshell.read.melee</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchshell.read.summon</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchshell.read.aura</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchshell.read.field</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Acid;Oil</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_etchshell</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z70" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>explode:1;linger:3</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>fw_corrode</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>fw_oilleak</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>fw_mix_nullmirror</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>fusion.nullmirror.name</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>8</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_nullmirror.desc</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>3</v>
+      </c>
+      <c r="M71" t="n">
+        <v>5</v>
+      </c>
+      <c r="N71" t="n">
+        <v>8</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_nullmirror.read.projectile</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_nullmirror.read.melee</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_nullmirror.read.summon</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_nullmirror.read.aura</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_nullmirror.read.field</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Apoptosis;Dark;Light;Mirror</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_nullmirror</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z71" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>explode:1;bounce:2</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>fw_execute</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>fw_deflect</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>fw_mix_mudshot</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>fusion.mudshot.name</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudshot.desc</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>3</v>
+      </c>
+      <c r="M72" t="n">
+        <v>2</v>
+      </c>
+      <c r="N72" t="n">
+        <v>6</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudshot.read.projectile</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudshot.read.melee</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudshot.read.summon</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudshot.read.aura</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudshot.read.field</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Earth;Wet</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_mudshot</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z72" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>lob:4;linger:3</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>fw_arc</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>fw_coolant</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>fw_mix_mudwave</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>fusion.mudwave.name</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudwave.desc</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>2</v>
+      </c>
+      <c r="M73" t="n">
+        <v>4</v>
+      </c>
+      <c r="N73" t="n">
+        <v>4</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudwave.read.projectile</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudwave.read.melee</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudwave.read.summon</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudwave.read.aura</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudwave.read.field</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Earth;Wet</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_mudwave</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z73" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>pull:0.5;grow:1</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>fw_tractor</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>fw_shockwave</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>fw_mix_rustbomb</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>fusion.rustbomb.name</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustbomb.desc</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>2</v>
+      </c>
+      <c r="M74" t="n">
+        <v>2</v>
+      </c>
+      <c r="N74" t="n">
+        <v>6</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustbomb.read.projectile</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustbomb.read.melee</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustbomb.read.summon</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustbomb.read.aura</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustbomb.read.field</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Poison;Blood</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_rustbomb</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z74" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>explode:1;linger:2;rhythm:2</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>fw_cluster</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>fw_clock</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>fw_mix_rustharvest</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>fusion.rustharvest.name</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustharvest.desc</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>3</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2</v>
+      </c>
+      <c r="N75" t="n">
+        <v>2</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustharvest.read.projectile</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustharvest.read.melee</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustharvest.read.summon</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustharvest.read.aura</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustharvest.read.field</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Poison;Blood</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_rustharvest</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z75" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>explode:1;linger:2;return:1</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>fw_cluster</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>fw_reclaim</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>fw_mix_steamshock</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>fusion.steamshock.name</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_steamshock.desc</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>2</v>
+      </c>
+      <c r="M76" t="n">
+        <v>2</v>
+      </c>
+      <c r="N76" t="n">
+        <v>7</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_steamshock.read.projectile</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_steamshock.read.melee</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_steamshock.read.summon</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_steamshock.read.aura</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_steamshock.read.field</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Wet;Fire</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_steamshock</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z76" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>grow:1;trail:2</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>fw_shockwave</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>fw_burntrail</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>fw_mix_floodarc</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>fusion.floodarc.name</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_floodarc.desc</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>3</v>
+      </c>
+      <c r="M77" t="n">
+        <v>3</v>
+      </c>
+      <c r="N77" t="n">
+        <v>6</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_floodarc.read.projectile</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_floodarc.read.melee</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_floodarc.read.summon</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_floodarc.read.aura</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_floodarc.read.field</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Capillary;Wet;Shock</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_floodarc</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z77" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>linger:3;scale:1.2;chain:2</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>fw_spread</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>fw_arcchain</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>em</t>
         </is>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
+++ b/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
@@ -4132,7 +4132,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Blood</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>Blood;Acid</t>
+          <t>Acid</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>Poison;Blood</t>
+          <t>Poison</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">

--- a/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
+++ b/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD77"/>
+  <dimension ref="A1:AD85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6948,7 +6948,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>fw_mix_napalm</t>
+          <t>fw_scuttle</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>fusion.napalm.name</t>
+          <t>firmware.fw_scuttle.name</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -6966,17 +6966,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>enemy</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>reclaim</t>
+          <t>foundry</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>fuse</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_napalm.desc</t>
+          <t>firmware.fw_scuttle.desc</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6995,90 +6995,90 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_napalm.read.projectile</t>
+          <t>firmware.fw_scuttle.read.projectile</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_napalm.read.melee</t>
+          <t>firmware.fw_scuttle.read.melee</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_napalm.read.summon</t>
+          <t>firmware.fw_scuttle.read.summon</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_napalm.read.aura</t>
+          <t>firmware.fw_scuttle.read.aura</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_napalm.read.field</t>
+          <t>firmware.fw_scuttle.read.field</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>Fire;Oil</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>icon_fw_mix_napalm</t>
+          <t>icon_fw_scuttle</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>fusion</t>
+          <t>salvage</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>firmware.acquire.fusion</t>
+          <t>firmware.acquire.salvage.foundry</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="Z48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>trail:2;linger:3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>fw_burntrail</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>fw_oilleak</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -7086,35 +7086,35 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>fw_mix_flashover</t>
+          <t>fw_bouncefuse</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>fusion.flashover.name</t>
+          <t>firmware.fw_bouncefuse.name</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>enemy</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>reclaim</t>
+          <t>foundry</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>limiter</t>
+          <t>fuse</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -7124,99 +7124,99 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_flashover.desc</t>
+          <t>firmware.fw_bouncefuse.desc</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>common</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_flashover.read.projectile</t>
+          <t>firmware.fw_bouncefuse.read.projectile</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_flashover.read.melee</t>
+          <t>firmware.fw_bouncefuse.read.melee</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_flashover.read.summon</t>
+          <t>firmware.fw_bouncefuse.read.summon</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_flashover.read.aura</t>
+          <t>firmware.fw_bouncefuse.read.aura</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_flashover.read.field</t>
+          <t>firmware.fw_bouncefuse.read.field</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>Fire;Oil</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>limiter</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>icon_fw_mix_flashover</t>
+          <t>icon_fw_bouncefuse</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>fusion</t>
+          <t>salvage</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>firmware.acquire.fusion</t>
+          <t>firmware.acquire.salvage.foundry</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="Z49" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>heatburst:1;linger:3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>fw_overload</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>fw_oilleak</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>fw_mix_steamjet</t>
+          <t>fw_piercefuse</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>fusion.steamjet.name</t>
+          <t>firmware.fw_piercefuse.name</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -7242,17 +7242,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>enemy</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>reclaim</t>
+          <t>foundry</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>fuse</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_steamjet.desc</t>
+          <t>firmware.fw_piercefuse.desc</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -7271,90 +7271,90 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_steamjet.read.projectile</t>
+          <t>firmware.fw_piercefuse.read.projectile</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_steamjet.read.melee</t>
+          <t>firmware.fw_piercefuse.read.melee</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_steamjet.read.summon</t>
+          <t>firmware.fw_piercefuse.read.summon</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_steamjet.read.aura</t>
+          <t>firmware.fw_piercefuse.read.aura</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_steamjet.read.field</t>
+          <t>firmware.fw_piercefuse.read.field</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>Fire;Wet</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>icon_fw_mix_steamjet</t>
+          <t>icon_fw_piercefuse</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>fusion</t>
+          <t>salvage</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>firmware.acquire.fusion</t>
+          <t>firmware.acquire.salvage.foundry</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="Z50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>trail:2;linger:3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>fw_burntrail</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>fw_coolant</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -7362,7 +7362,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>fw_mix_cryoflame</t>
+          <t>fw_ventarc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>fusion.cryoflame.name</t>
+          <t>firmware.fw_ventarc.name</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -7380,17 +7380,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>enemy</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>reclaim</t>
+          <t>silent</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>em</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -7400,99 +7400,99 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_cryoflame.desc</t>
+          <t>firmware.fw_ventarc.desc</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N51" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_cryoflame.read.projectile</t>
+          <t>firmware.fw_ventarc.read.projectile</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_cryoflame.read.melee</t>
+          <t>firmware.fw_ventarc.read.melee</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_cryoflame.read.summon</t>
+          <t>firmware.fw_ventarc.read.summon</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_cryoflame.read.aura</t>
+          <t>firmware.fw_ventarc.read.aura</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_cryoflame.read.field</t>
+          <t>firmware.fw_ventarc.read.field</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>Fire;Frozen</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>em</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>icon_fw_mix_cryoflame</t>
+          <t>icon_fw_ventarc</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>fusion</t>
+          <t>salvage</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>firmware.acquire.fusion</t>
+          <t>firmware.acquire.salvage.silent</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="Z51" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>trail:2;linger:3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>fw_burntrail</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>fw_nitrogen</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -7500,35 +7500,35 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>fw_mix_thermalspike</t>
+          <t>fw_coolback</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>fusion.thermalspike.name</t>
+          <t>firmware.fw_coolback.name</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>enemy</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>reclaim</t>
+          <t>clarity</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>limiter</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -7538,99 +7538,99 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_thermalspike.desc</t>
+          <t>firmware.fw_coolback.desc</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>common</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_thermalspike.read.projectile</t>
+          <t>firmware.fw_coolback.read.projectile</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_thermalspike.read.melee</t>
+          <t>firmware.fw_coolback.read.melee</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_thermalspike.read.summon</t>
+          <t>firmware.fw_coolback.read.summon</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_thermalspike.read.aura</t>
+          <t>firmware.fw_coolback.read.aura</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_thermalspike.read.field</t>
+          <t>firmware.fw_coolback.read.field</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>Fire;Frozen</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>limiter</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>icon_fw_mix_thermalspike</t>
+          <t>icon_fw_coolback</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>fusion</t>
+          <t>salvage</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>firmware.acquire.fusion</t>
+          <t>firmware.acquire.salvage.clarity</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="Z52" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>heatburst:1;linger:3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>fw_overload</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>fw_nitrogen</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>fw_mix_causticflame</t>
+          <t>fw_enterfuse</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>fusion.causticflame.name</t>
+          <t>firmware.fw_enterfuse.name</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -7656,17 +7656,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>enemy</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>reclaim</t>
+          <t>foundry</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>fuse</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -7676,99 +7676,99 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_causticflame.desc</t>
+          <t>firmware.fw_enterfuse.desc</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_causticflame.read.projectile</t>
+          <t>firmware.fw_enterfuse.read.projectile</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_causticflame.read.melee</t>
+          <t>firmware.fw_enterfuse.read.melee</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_causticflame.read.summon</t>
+          <t>firmware.fw_enterfuse.read.summon</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_causticflame.read.aura</t>
+          <t>firmware.fw_enterfuse.read.aura</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_causticflame.read.field</t>
+          <t>firmware.fw_enterfuse.read.field</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>Fire;Acid</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>icon_fw_mix_causticflame</t>
+          <t>icon_fw_enterfuse</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>fusion</t>
+          <t>salvage</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>firmware.acquire.fusion</t>
+          <t>firmware.acquire.salvage.foundry</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="Z53" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>trail:2;linger:3</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>fw_burntrail</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>fw_acid</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -7776,7 +7776,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>fw_mix_causticshell</t>
+          <t>fw_uplinkpulse</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>fusion.causticshell.name</t>
+          <t>firmware.fw_uplinkpulse.name</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -7794,17 +7794,17 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>enemy</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>reclaim</t>
+          <t>silent</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>fuse</t>
+          <t>em</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -7814,99 +7814,99 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_causticshell.desc</t>
+          <t>firmware.fw_uplinkpulse.desc</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="n">
         <v>2</v>
       </c>
-      <c r="M54" t="n">
-        <v>1</v>
-      </c>
       <c r="N54" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_causticshell.read.projectile</t>
+          <t>firmware.fw_uplinkpulse.read.projectile</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_causticshell.read.melee</t>
+          <t>firmware.fw_uplinkpulse.read.melee</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_causticshell.read.summon</t>
+          <t>firmware.fw_uplinkpulse.read.summon</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_causticshell.read.aura</t>
+          <t>firmware.fw_uplinkpulse.read.aura</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_causticshell.read.field</t>
+          <t>firmware.fw_uplinkpulse.read.field</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>Acid;Fire</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>em</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>icon_fw_mix_causticshell</t>
+          <t>icon_fw_uplinkpulse</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>fusion</t>
+          <t>salvage</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>firmware.acquire.fusion</t>
+          <t>firmware.acquire.salvage.silent</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>explode:1;trail:2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>fw_corrode</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>fw_burntrail</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>fw_mix_glassburst</t>
+          <t>fw_water</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>fusion.glassburst.name</t>
+          <t>firmware.fw_water.name</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -7932,17 +7932,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>own</t>
+          <t>enemy</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>reclaim</t>
+          <t>clarity</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>fuse</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -7952,99 +7952,99 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_glassburst.desc</t>
+          <t>firmware.fw_water.desc</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>common</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
         <v>2</v>
       </c>
-      <c r="N55" t="n">
-        <v>7</v>
-      </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_glassburst.read.projectile</t>
+          <t>firmware.fw_water.read.projectile</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_glassburst.read.melee</t>
+          <t>firmware.fw_water.read.melee</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_glassburst.read.summon</t>
+          <t>firmware.fw_water.read.summon</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_glassburst.read.aura</t>
+          <t>firmware.fw_water.read.aura</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_glassburst.read.field</t>
+          <t>firmware.fw_water.read.field</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>Earth;Fire</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>icon_fw_mix_glassburst</t>
+          <t>icon_fw_water</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>fusion</t>
+          <t>salvage</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>firmware.acquire.fusion</t>
+          <t>firmware.acquire.salvage.clarity</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>lob:4;trail:2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>fw_arc</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>fw_burntrail</t>
+          <t>none</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>none</t>
         </is>
       </c>
     </row>
@@ -8052,7 +8052,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>fw_mix_cinderpull</t>
+          <t>fw_mix_napalm</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>fusion.cinderpull.name</t>
+          <t>fusion.napalm.name</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>em</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -8090,61 +8090,61 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_cinderpull.desc</t>
+          <t>firmware.fw_mix_napalm.desc</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="L56" t="n">
         <v>2</v>
       </c>
       <c r="M56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
         <v>7</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_cinderpull.read.projectile</t>
+          <t>firmware.fw_mix_napalm.read.projectile</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_cinderpull.read.melee</t>
+          <t>firmware.fw_mix_napalm.read.melee</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_cinderpull.read.summon</t>
+          <t>firmware.fw_mix_napalm.read.summon</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_cinderpull.read.aura</t>
+          <t>firmware.fw_mix_napalm.read.aura</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_cinderpull.read.field</t>
+          <t>firmware.fw_mix_napalm.read.field</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>Earth;Fire</t>
+          <t>Fire;Oil</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>em</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>icon_fw_mix_cinderpull</t>
+          <t>icon_fw_mix_napalm</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -8163,21 +8163,21 @@
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>pull:0.5;trail:2</t>
+          <t>trail:2;linger:3</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>fw_tractor</t>
+          <t>fw_burntrail</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>fw_burntrail</t>
+          <t>fw_oilleak</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
@@ -8190,21 +8190,21 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>fw_mix_wetarc</t>
+          <t>fw_mix_flashover</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>core</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>fusion.wetarc.name</t>
+          <t>fusion.flashover.name</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>em</t>
+          <t>limiter</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -8228,61 +8228,61 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_wetarc.desc</t>
+          <t>firmware.fw_mix_flashover.desc</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="L57" t="n">
         <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_wetarc.read.projectile</t>
+          <t>firmware.fw_mix_flashover.read.projectile</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_wetarc.read.melee</t>
+          <t>firmware.fw_mix_flashover.read.melee</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_wetarc.read.summon</t>
+          <t>firmware.fw_mix_flashover.read.summon</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_wetarc.read.aura</t>
+          <t>firmware.fw_mix_flashover.read.aura</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_wetarc.read.field</t>
+          <t>firmware.fw_mix_flashover.read.field</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>Shock;Wet</t>
+          <t>Fire;Oil</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>em</t>
+          <t>limiter</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>icon_fw_mix_wetarc</t>
+          <t>icon_fw_mix_flashover</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
@@ -8301,21 +8301,21 @@
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>chain:2;linger:3</t>
+          <t>heatburst:1;linger:3</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>fw_arcchain</t>
+          <t>fw_overload</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>fw_coolant</t>
+          <t>fw_oilleak</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
@@ -8328,7 +8328,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>fw_mix_stormwave</t>
+          <t>fw_mix_steamjet</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>fusion.stormwave.name</t>
+          <t>fusion.steamjet.name</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>em</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_stormwave.desc</t>
+          <t>firmware.fw_mix_steamjet.desc</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -8378,49 +8378,49 @@
         <v>2</v>
       </c>
       <c r="M58" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_stormwave.read.projectile</t>
+          <t>firmware.fw_mix_steamjet.read.projectile</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_stormwave.read.melee</t>
+          <t>firmware.fw_mix_steamjet.read.melee</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_stormwave.read.summon</t>
+          <t>firmware.fw_mix_steamjet.read.summon</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_stormwave.read.aura</t>
+          <t>firmware.fw_mix_steamjet.read.aura</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_stormwave.read.field</t>
+          <t>firmware.fw_mix_steamjet.read.field</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>Wet;Shock</t>
+          <t>Fire;Wet</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>em</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>icon_fw_mix_stormwave</t>
+          <t>icon_fw_mix_steamjet</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
@@ -8443,22 +8443,22 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>grow:1;chain:2</t>
+          <t>trail:2;linger:3</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>fw_shockwave</t>
+          <t>fw_burntrail</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>fw_arcchain</t>
+          <t>fw_coolant</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>em</t>
+          <t>fluid</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>fw_mix_shortloop</t>
+          <t>fw_mix_cryoflame</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>fusion.shortloop.name</t>
+          <t>fusion.cryoflame.name</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>limiter</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -8504,61 +8504,61 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_shortloop.desc</t>
+          <t>firmware.fw_mix_cryoflame.desc</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_shortloop.read.projectile</t>
+          <t>firmware.fw_mix_cryoflame.read.projectile</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_shortloop.read.melee</t>
+          <t>firmware.fw_mix_cryoflame.read.melee</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_shortloop.read.summon</t>
+          <t>firmware.fw_mix_cryoflame.read.summon</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_shortloop.read.aura</t>
+          <t>firmware.fw_mix_cryoflame.read.aura</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_shortloop.read.field</t>
+          <t>firmware.fw_mix_cryoflame.read.field</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>Shock;Wet</t>
+          <t>Fire;Frozen</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>limiter</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>icon_fw_mix_shortloop</t>
+          <t>icon_fw_mix_cryoflame</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
@@ -8577,21 +8577,21 @@
         </is>
       </c>
       <c r="Z59" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>feedback:0.2;linger:3</t>
+          <t>trail:2;linger:3</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>fw_followup</t>
+          <t>fw_burntrail</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>fw_coolant</t>
+          <t>fw_nitrogen</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -8604,21 +8604,21 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>fw_mix_electrolyte</t>
+          <t>fw_mix_thermalspike</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>core</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>fusion.electrolyte.name</t>
+          <t>fusion.thermalspike.name</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>em</t>
+          <t>limiter</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -8642,61 +8642,61 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_electrolyte.desc</t>
+          <t>firmware.fw_mix_thermalspike.desc</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="L60" t="n">
         <v>2</v>
       </c>
       <c r="M60" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_electrolyte.read.projectile</t>
+          <t>firmware.fw_mix_thermalspike.read.projectile</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_electrolyte.read.melee</t>
+          <t>firmware.fw_mix_thermalspike.read.melee</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_electrolyte.read.summon</t>
+          <t>firmware.fw_mix_thermalspike.read.summon</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_electrolyte.read.aura</t>
+          <t>firmware.fw_mix_thermalspike.read.aura</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_electrolyte.read.field</t>
+          <t>firmware.fw_mix_thermalspike.read.field</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>Shock;Acid</t>
+          <t>Fire;Frozen</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>em</t>
+          <t>limiter</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>icon_fw_mix_electrolyte</t>
+          <t>icon_fw_mix_thermalspike</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="Z60" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>chain:2;linger:3</t>
+          <t>heatburst:1;linger:3</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>fw_arcchain</t>
+          <t>fw_overload</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>fw_acid</t>
+          <t>fw_nitrogen</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
@@ -8742,7 +8742,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>fw_mix_ioncorrode</t>
+          <t>fw_mix_causticflame</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>fusion.ioncorrode.name</t>
+          <t>fusion.causticflame.name</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>limiter</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -8780,61 +8780,61 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_ioncorrode.desc</t>
+          <t>firmware.fw_mix_causticflame.desc</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M61" t="n">
         <v>2</v>
       </c>
       <c r="N61" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_ioncorrode.read.projectile</t>
+          <t>firmware.fw_mix_causticflame.read.projectile</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_ioncorrode.read.melee</t>
+          <t>firmware.fw_mix_causticflame.read.melee</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_ioncorrode.read.summon</t>
+          <t>firmware.fw_mix_causticflame.read.summon</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_ioncorrode.read.aura</t>
+          <t>firmware.fw_mix_causticflame.read.aura</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_ioncorrode.read.field</t>
+          <t>firmware.fw_mix_causticflame.read.field</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>Shock;Acid</t>
+          <t>Fire;Acid</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>limiter</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>icon_fw_mix_ioncorrode</t>
+          <t>icon_fw_mix_causticflame</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -8853,26 +8853,26 @@
         </is>
       </c>
       <c r="Z61" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>feedback:0.2;explode:1</t>
+          <t>trail:2;linger:3</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>fw_followup</t>
+          <t>fw_burntrail</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>fw_corrode</t>
+          <t>fw_acid</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>fuse</t>
+          <t>fluid</t>
         </is>
       </c>
     </row>
@@ -8880,7 +8880,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>fw_mix_insulfoam</t>
+          <t>fw_mix_causticshell</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>fusion.insulfoam.name</t>
+          <t>fusion.causticshell.name</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>em</t>
+          <t>fuse</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -8918,61 +8918,61 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_insulfoam.desc</t>
+          <t>firmware.fw_mix_causticshell.desc</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="L62" t="n">
         <v>2</v>
       </c>
       <c r="M62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_insulfoam.read.projectile</t>
+          <t>firmware.fw_mix_causticshell.read.projectile</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_insulfoam.read.melee</t>
+          <t>firmware.fw_mix_causticshell.read.melee</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_insulfoam.read.summon</t>
+          <t>firmware.fw_mix_causticshell.read.summon</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_insulfoam.read.aura</t>
+          <t>firmware.fw_mix_causticshell.read.aura</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_insulfoam.read.field</t>
+          <t>firmware.fw_mix_causticshell.read.field</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>Shock;Oil</t>
+          <t>Acid;Fire</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>em</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>icon_fw_mix_insulfoam</t>
+          <t>icon_fw_mix_causticshell</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -8991,21 +8991,21 @@
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>chain:2;linger:3</t>
+          <t>explode:1;trail:2</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>fw_arcchain</t>
+          <t>fw_corrode</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>fw_oilleak</t>
+          <t>fw_burntrail</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
@@ -9018,7 +9018,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>fw_mix_gumacid</t>
+          <t>fw_mix_glassburst</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>fusion.gumacid.name</t>
+          <t>fusion.glassburst.name</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>fuse</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -9056,61 +9056,61 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_gumacid.desc</t>
+          <t>firmware.fw_mix_glassburst.desc</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M63" t="n">
         <v>2</v>
       </c>
       <c r="N63" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_gumacid.read.projectile</t>
+          <t>firmware.fw_mix_glassburst.read.projectile</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_gumacid.read.melee</t>
+          <t>firmware.fw_mix_glassburst.read.melee</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_gumacid.read.summon</t>
+          <t>firmware.fw_mix_glassburst.read.summon</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_gumacid.read.aura</t>
+          <t>firmware.fw_mix_glassburst.read.aura</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_gumacid.read.field</t>
+          <t>firmware.fw_mix_glassburst.read.field</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>Acid;SugarFilm</t>
+          <t>Earth;Fire</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>icon_fw_mix_gumacid</t>
+          <t>icon_fw_mix_glassburst</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
@@ -9129,21 +9129,21 @@
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>linger:4.5</t>
+          <t>lob:4;trail:2</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>fw_acid</t>
+          <t>fw_arc</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>fw_adhesive</t>
+          <t>fw_burntrail</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
@@ -9156,7 +9156,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>fw_mix_stickyshell</t>
+          <t>fw_mix_cinderpull</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>fusion.stickyshell.name</t>
+          <t>fusion.cinderpull.name</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>fuse</t>
+          <t>em</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_stickyshell.desc</t>
+          <t>firmware.fw_mix_cinderpull.desc</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -9206,49 +9206,49 @@
         <v>2</v>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N64" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_stickyshell.read.projectile</t>
+          <t>firmware.fw_mix_cinderpull.read.projectile</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_stickyshell.read.melee</t>
+          <t>firmware.fw_mix_cinderpull.read.melee</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_stickyshell.read.summon</t>
+          <t>firmware.fw_mix_cinderpull.read.summon</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_stickyshell.read.aura</t>
+          <t>firmware.fw_mix_cinderpull.read.aura</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_stickyshell.read.field</t>
+          <t>firmware.fw_mix_cinderpull.read.field</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>Acid;SugarFilm</t>
+          <t>Earth;Fire</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>em</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>icon_fw_mix_stickyshell</t>
+          <t>icon_fw_mix_cinderpull</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
@@ -9271,17 +9271,17 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>explode:1;linger:3</t>
+          <t>pull:0.5;trail:2</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>fw_corrode</t>
+          <t>fw_tractor</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>fw_adhesive</t>
+          <t>fw_burntrail</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
@@ -9294,7 +9294,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>fw_mix_rustclock</t>
+          <t>fw_mix_wetarc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>fusion.rustclock.name</t>
+          <t>fusion.wetarc.name</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -9322,7 +9322,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>limiter</t>
+          <t>em</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -9332,12 +9332,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_rustclock.desc</t>
+          <t>firmware.fw_mix_wetarc.desc</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="L65" t="n">
@@ -9351,42 +9351,42 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_rustclock.read.projectile</t>
+          <t>firmware.fw_mix_wetarc.read.projectile</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_rustclock.read.melee</t>
+          <t>firmware.fw_mix_wetarc.read.melee</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_rustclock.read.summon</t>
+          <t>firmware.fw_mix_wetarc.read.summon</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_rustclock.read.aura</t>
+          <t>firmware.fw_mix_wetarc.read.aura</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_rustclock.read.field</t>
+          <t>firmware.fw_mix_wetarc.read.field</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>Acid</t>
+          <t>Shock;Wet</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>limiter</t>
+          <t>em</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>icon_fw_mix_rustclock</t>
+          <t>icon_fw_mix_wetarc</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
@@ -9405,21 +9405,21 @@
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>rhythm:2;linger:3</t>
+          <t>chain:2;linger:3</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>fw_clock</t>
+          <t>fw_arcchain</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>fw_acid</t>
+          <t>fw_coolant</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
@@ -9432,7 +9432,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>fw_mix_meltreclaim</t>
+          <t>fw_mix_stormwave</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>fusion.meltreclaim.name</t>
+          <t>fusion.stormwave.name</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>limiter</t>
+          <t>em</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -9470,61 +9470,61 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_meltreclaim.desc</t>
+          <t>firmware.fw_mix_stormwave.desc</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>common</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_meltreclaim.read.projectile</t>
+          <t>firmware.fw_mix_stormwave.read.projectile</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_meltreclaim.read.melee</t>
+          <t>firmware.fw_mix_stormwave.read.melee</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_meltreclaim.read.summon</t>
+          <t>firmware.fw_mix_stormwave.read.summon</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_meltreclaim.read.aura</t>
+          <t>firmware.fw_mix_stormwave.read.aura</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_meltreclaim.read.field</t>
+          <t>firmware.fw_mix_stormwave.read.field</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>Blood;Acid</t>
+          <t>Wet;Shock</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>limiter</t>
+          <t>em</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>icon_fw_mix_meltreclaim</t>
+          <t>icon_fw_mix_stormwave</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -9543,26 +9543,26 @@
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>return:1;explode:1</t>
+          <t>grow:1;chain:2</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>fw_reclaim</t>
+          <t>fw_shockwave</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>fw_corrode</t>
+          <t>fw_arcchain</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>fuse</t>
+          <t>em</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9570,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>fw_mix_bindflow</t>
+          <t>fw_mix_shortloop</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>fusion.bindflow.name</t>
+          <t>fusion.shortloop.name</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>limiter</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -9608,61 +9608,61 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_bindflow.desc</t>
+          <t>firmware.fw_mix_shortloop.desc</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N67" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_bindflow.read.projectile</t>
+          <t>firmware.fw_mix_shortloop.read.projectile</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_bindflow.read.melee</t>
+          <t>firmware.fw_mix_shortloop.read.melee</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_bindflow.read.summon</t>
+          <t>firmware.fw_mix_shortloop.read.summon</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_bindflow.read.aura</t>
+          <t>firmware.fw_mix_shortloop.read.aura</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_bindflow.read.field</t>
+          <t>firmware.fw_mix_shortloop.read.field</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>Wet;SugarFilm</t>
+          <t>Shock;Wet</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>limiter</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>icon_fw_mix_bindflow</t>
+          <t>icon_fw_mix_shortloop</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
@@ -9681,21 +9681,21 @@
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>linger:4.5</t>
+          <t>feedback:0.2;linger:3</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
+          <t>fw_followup</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
           <t>fw_coolant</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>fw_adhesive</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
@@ -9708,7 +9708,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>fw_mix_bindspread</t>
+          <t>fw_mix_electrolyte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>fusion.bindspread.name</t>
+          <t>fusion.electrolyte.name</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>em</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -9746,61 +9746,61 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_bindspread.desc</t>
+          <t>firmware.fw_mix_electrolyte.desc</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N68" t="n">
         <v>5</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_bindspread.read.projectile</t>
+          <t>firmware.fw_mix_electrolyte.read.projectile</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_bindspread.read.melee</t>
+          <t>firmware.fw_mix_electrolyte.read.melee</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_bindspread.read.summon</t>
+          <t>firmware.fw_mix_electrolyte.read.summon</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_bindspread.read.aura</t>
+          <t>firmware.fw_mix_electrolyte.read.aura</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_bindspread.read.field</t>
+          <t>firmware.fw_mix_electrolyte.read.field</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>Capillary;Wet;SugarFilm</t>
+          <t>Shock;Acid</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>em</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>icon_fw_mix_bindspread</t>
+          <t>icon_fw_mix_electrolyte</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
@@ -9819,21 +9819,21 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>linger:4.5;scale:1.2</t>
+          <t>chain:2;linger:3</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>fw_spread</t>
+          <t>fw_arcchain</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>fw_adhesive</t>
+          <t>fw_acid</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr">
@@ -9846,7 +9846,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>fw_mix_etchslick</t>
+          <t>fw_mix_ioncorrode</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>fusion.etchslick.name</t>
+          <t>fusion.ioncorrode.name</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>limiter</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -9884,61 +9884,61 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_etchslick.desc</t>
+          <t>firmware.fw_mix_ioncorrode.desc</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M69" t="n">
         <v>2</v>
       </c>
       <c r="N69" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_etchslick.read.projectile</t>
+          <t>firmware.fw_mix_ioncorrode.read.projectile</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_etchslick.read.melee</t>
+          <t>firmware.fw_mix_ioncorrode.read.melee</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_etchslick.read.summon</t>
+          <t>firmware.fw_mix_ioncorrode.read.summon</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_etchslick.read.aura</t>
+          <t>firmware.fw_mix_ioncorrode.read.aura</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_etchslick.read.field</t>
+          <t>firmware.fw_mix_ioncorrode.read.field</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>Acid;Oil</t>
+          <t>Shock;Acid</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>limiter</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>icon_fw_mix_etchslick</t>
+          <t>icon_fw_mix_ioncorrode</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
@@ -9957,26 +9957,26 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>linger:4.5</t>
+          <t>feedback:0.2;explode:1</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>fw_acid</t>
+          <t>fw_followup</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>fw_oilleak</t>
+          <t>fw_corrode</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>fluid</t>
+          <t>fuse</t>
         </is>
       </c>
     </row>
@@ -9984,7 +9984,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>fw_mix_etchshell</t>
+          <t>fw_mix_insulfoam</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -9994,7 +9994,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>fusion.etchshell.name</t>
+          <t>fusion.insulfoam.name</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>fuse</t>
+          <t>em</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -10022,61 +10022,61 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_etchshell.desc</t>
+          <t>firmware.fw_mix_insulfoam.desc</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>common</t>
         </is>
       </c>
       <c r="L70" t="n">
         <v>2</v>
       </c>
       <c r="M70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_etchshell.read.projectile</t>
+          <t>firmware.fw_mix_insulfoam.read.projectile</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_etchshell.read.melee</t>
+          <t>firmware.fw_mix_insulfoam.read.melee</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_etchshell.read.summon</t>
+          <t>firmware.fw_mix_insulfoam.read.summon</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_etchshell.read.aura</t>
+          <t>firmware.fw_mix_insulfoam.read.aura</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_etchshell.read.field</t>
+          <t>firmware.fw_mix_insulfoam.read.field</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>Acid;Oil</t>
+          <t>Shock;Oil</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>em</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>icon_fw_mix_etchshell</t>
+          <t>icon_fw_mix_insulfoam</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
@@ -10095,16 +10095,16 @@
         </is>
       </c>
       <c r="Z70" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>explode:1;linger:3</t>
+          <t>chain:2;linger:3</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>fw_corrode</t>
+          <t>fw_arcchain</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -10122,21 +10122,21 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>fw_mix_nullmirror</t>
+          <t>fw_mix_gumacid</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>fusion.nullmirror.name</t>
+          <t>fusion.gumacid.name</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>limiter</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -10160,61 +10160,61 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_nullmirror.desc</t>
+          <t>firmware.fw_mix_gumacid.desc</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N71" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_nullmirror.read.projectile</t>
+          <t>firmware.fw_mix_gumacid.read.projectile</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_nullmirror.read.melee</t>
+          <t>firmware.fw_mix_gumacid.read.melee</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_nullmirror.read.summon</t>
+          <t>firmware.fw_mix_gumacid.read.summon</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_nullmirror.read.aura</t>
+          <t>firmware.fw_mix_gumacid.read.aura</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_nullmirror.read.field</t>
+          <t>firmware.fw_mix_gumacid.read.field</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>Apoptosis;Dark;Light;Mirror</t>
+          <t>Acid;SugarFilm</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>limiter</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>icon_fw_mix_nullmirror</t>
+          <t>icon_fw_mix_gumacid</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
@@ -10233,26 +10233,26 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>explode:1;bounce:2</t>
+          <t>linger:4.5</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>fw_execute</t>
+          <t>fw_acid</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>fw_deflect</t>
+          <t>fw_adhesive</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>em</t>
+          <t>fluid</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10260,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>fw_mix_mudshot</t>
+          <t>fw_mix_stickyshell</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -10270,7 +10270,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>fusion.mudshot.name</t>
+          <t>fusion.stickyshell.name</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -10298,51 +10298,51 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_mudshot.desc</t>
+          <t>firmware.fw_mix_stickyshell.desc</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="L72" t="n">
+        <v>2</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1</v>
+      </c>
+      <c r="N72" t="n">
         <v>3</v>
       </c>
-      <c r="M72" t="n">
-        <v>2</v>
-      </c>
-      <c r="N72" t="n">
-        <v>6</v>
-      </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_mudshot.read.projectile</t>
+          <t>firmware.fw_mix_stickyshell.read.projectile</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_mudshot.read.melee</t>
+          <t>firmware.fw_mix_stickyshell.read.melee</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_mudshot.read.summon</t>
+          <t>firmware.fw_mix_stickyshell.read.summon</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_mudshot.read.aura</t>
+          <t>firmware.fw_mix_stickyshell.read.aura</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_mudshot.read.field</t>
+          <t>firmware.fw_mix_stickyshell.read.field</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>Earth;Wet</t>
+          <t>Acid;SugarFilm</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>icon_fw_mix_mudshot</t>
+          <t>icon_fw_mix_stickyshell</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
@@ -10371,21 +10371,21 @@
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>lob:4;linger:3</t>
+          <t>explode:1;linger:3</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>fw_arc</t>
+          <t>fw_corrode</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>fw_coolant</t>
+          <t>fw_adhesive</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr">
@@ -10398,7 +10398,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>fw_mix_mudwave</t>
+          <t>fw_mix_rustclock</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>fusion.mudwave.name</t>
+          <t>fusion.rustclock.name</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>em</t>
+          <t>limiter</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_mudwave.desc</t>
+          <t>firmware.fw_mix_rustclock.desc</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -10448,49 +10448,49 @@
         <v>2</v>
       </c>
       <c r="M73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N73" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_mudwave.read.projectile</t>
+          <t>firmware.fw_mix_rustclock.read.projectile</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_mudwave.read.melee</t>
+          <t>firmware.fw_mix_rustclock.read.melee</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_mudwave.read.summon</t>
+          <t>firmware.fw_mix_rustclock.read.summon</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_mudwave.read.aura</t>
+          <t>firmware.fw_mix_rustclock.read.aura</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_mudwave.read.field</t>
+          <t>firmware.fw_mix_rustclock.read.field</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>Earth;Wet</t>
+          <t>Acid</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>em</t>
+          <t>limiter</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>icon_fw_mix_mudwave</t>
+          <t>icon_fw_mix_rustclock</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -10513,22 +10513,22 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>pull:0.5;grow:1</t>
+          <t>rhythm:2;linger:3</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>fw_tractor</t>
+          <t>fw_clock</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>fw_shockwave</t>
+          <t>fw_acid</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>em</t>
+          <t>fluid</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>fw_mix_rustbomb</t>
+          <t>fw_mix_meltreclaim</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10546,7 +10546,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>fusion.rustbomb.name</t>
+          <t>fusion.meltreclaim.name</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -10564,7 +10564,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>fuse</t>
+          <t>limiter</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -10574,61 +10574,61 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_rustbomb.desc</t>
+          <t>firmware.fw_mix_meltreclaim.desc</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>rare</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M74" t="n">
         <v>2</v>
       </c>
       <c r="N74" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_rustbomb.read.projectile</t>
+          <t>firmware.fw_mix_meltreclaim.read.projectile</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_rustbomb.read.melee</t>
+          <t>firmware.fw_mix_meltreclaim.read.melee</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_rustbomb.read.summon</t>
+          <t>firmware.fw_mix_meltreclaim.read.summon</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_rustbomb.read.aura</t>
+          <t>firmware.fw_mix_meltreclaim.read.aura</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_rustbomb.read.field</t>
+          <t>firmware.fw_mix_meltreclaim.read.field</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>Poison</t>
+          <t>Blood;Acid</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>limiter</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>icon_fw_mix_rustbomb</t>
+          <t>icon_fw_mix_meltreclaim</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -10647,26 +10647,26 @@
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>explode:1;linger:2;rhythm:2</t>
+          <t>return:1;explode:1</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>fw_cluster</t>
+          <t>fw_reclaim</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>fw_clock</t>
+          <t>fw_corrode</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>limiter</t>
+          <t>fuse</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>fw_mix_rustharvest</t>
+          <t>fw_mix_bindflow</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>fusion.rustharvest.name</t>
+          <t>fusion.bindflow.name</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>fuse</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -10712,61 +10712,61 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_rustharvest.desc</t>
+          <t>firmware.fw_mix_bindflow.desc</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>epic</t>
+          <t>common</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_rustharvest.read.projectile</t>
+          <t>firmware.fw_mix_bindflow.read.projectile</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_rustharvest.read.melee</t>
+          <t>firmware.fw_mix_bindflow.read.melee</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_rustharvest.read.summon</t>
+          <t>firmware.fw_mix_bindflow.read.summon</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_rustharvest.read.aura</t>
+          <t>firmware.fw_mix_bindflow.read.aura</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_rustharvest.read.field</t>
+          <t>firmware.fw_mix_bindflow.read.field</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>Poison;Blood</t>
+          <t>Wet;SugarFilm</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>icon_fw_mix_rustharvest</t>
+          <t>icon_fw_mix_bindflow</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
@@ -10785,26 +10785,26 @@
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>explode:1;linger:2;return:1</t>
+          <t>linger:4.5</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>fw_cluster</t>
+          <t>fw_coolant</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>fw_reclaim</t>
+          <t>fw_adhesive</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>limiter</t>
+          <t>fluid</t>
         </is>
       </c>
     </row>
@@ -10812,7 +10812,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>fw_mix_steamshock</t>
+          <t>fw_mix_bindspread</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -10822,7 +10822,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>fusion.steamshock.name</t>
+          <t>fusion.bindspread.name</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -10840,7 +10840,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>em</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -10850,61 +10850,61 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_steamshock.desc</t>
+          <t>firmware.fw_mix_bindspread.desc</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>epic</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_steamshock.read.projectile</t>
+          <t>firmware.fw_mix_bindspread.read.projectile</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_steamshock.read.melee</t>
+          <t>firmware.fw_mix_bindspread.read.melee</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_steamshock.read.summon</t>
+          <t>firmware.fw_mix_bindspread.read.summon</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_steamshock.read.aura</t>
+          <t>firmware.fw_mix_bindspread.read.aura</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>firmware.fw_mix_steamshock.read.field</t>
+          <t>firmware.fw_mix_bindspread.read.field</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>Wet;Fire</t>
+          <t>Capillary;Wet;SugarFilm</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>em</t>
+          <t>fluid</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>icon_fw_mix_steamshock</t>
+          <t>icon_fw_mix_bindspread</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -10923,21 +10923,21 @@
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>grow:1;trail:2</t>
+          <t>linger:4.5;scale:1.2</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>fw_shockwave</t>
+          <t>fw_spread</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>fw_burntrail</t>
+          <t>fw_adhesive</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr">
@@ -10950,7 +10950,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>fw_mix_floodarc</t>
+          <t>fw_mix_etchslick</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>fusion.floodarc.name</t>
+          <t>fusion.etchslick.name</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -10988,97 +10988,1201 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t>firmware.fw_mix_etchslick.desc</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>2</v>
+      </c>
+      <c r="M77" t="n">
+        <v>2</v>
+      </c>
+      <c r="N77" t="n">
+        <v>4</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchslick.read.projectile</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchslick.read.melee</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchslick.read.summon</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchslick.read.aura</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchslick.read.field</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Acid;Oil</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_etchslick</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z77" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>linger:4.5</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>fw_acid</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>fw_oilleak</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>fw_mix_etchshell</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>fusion.etchshell.name</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchshell.desc</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>2</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" t="n">
+        <v>3</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchshell.read.projectile</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchshell.read.melee</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchshell.read.summon</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchshell.read.aura</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_etchshell.read.field</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Acid;Oil</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_etchshell</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z78" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>explode:1;linger:3</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>fw_corrode</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>fw_oilleak</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>fw_mix_nullmirror</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>fusion.nullmirror.name</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>8</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_nullmirror.desc</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>3</v>
+      </c>
+      <c r="M79" t="n">
+        <v>5</v>
+      </c>
+      <c r="N79" t="n">
+        <v>8</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_nullmirror.read.projectile</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_nullmirror.read.melee</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_nullmirror.read.summon</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_nullmirror.read.aura</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_nullmirror.read.field</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Apoptosis;Dark;Light;Mirror</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_nullmirror</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z79" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>explode:1;bounce:2</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>fw_execute</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>fw_deflect</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>fw_mix_mudshot</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>fusion.mudshot.name</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudshot.desc</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>3</v>
+      </c>
+      <c r="M80" t="n">
+        <v>2</v>
+      </c>
+      <c r="N80" t="n">
+        <v>6</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudshot.read.projectile</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudshot.read.melee</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudshot.read.summon</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudshot.read.aura</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudshot.read.field</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Earth;Wet</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_mudshot</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z80" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>lob:4;linger:3</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>fw_arc</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>fw_coolant</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>fw_mix_mudwave</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>fusion.mudwave.name</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudwave.desc</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>2</v>
+      </c>
+      <c r="M81" t="n">
+        <v>4</v>
+      </c>
+      <c r="N81" t="n">
+        <v>4</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudwave.read.projectile</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudwave.read.melee</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudwave.read.summon</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudwave.read.aura</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_mudwave.read.field</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Earth;Wet</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_mudwave</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z81" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>pull:0.5;grow:1</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>fw_tractor</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>fw_shockwave</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>fw_mix_rustbomb</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>fusion.rustbomb.name</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustbomb.desc</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>rare</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>2</v>
+      </c>
+      <c r="M82" t="n">
+        <v>2</v>
+      </c>
+      <c r="N82" t="n">
+        <v>6</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustbomb.read.projectile</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustbomb.read.melee</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustbomb.read.summon</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustbomb.read.aura</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustbomb.read.field</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Poison</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_rustbomb</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z82" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>explode:1;linger:2;rhythm:2</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>fw_cluster</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>fw_clock</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>fw_mix_rustharvest</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>fusion.rustharvest.name</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustharvest.desc</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>epic</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>3</v>
+      </c>
+      <c r="M83" t="n">
+        <v>2</v>
+      </c>
+      <c r="N83" t="n">
+        <v>2</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustharvest.read.projectile</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustharvest.read.melee</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustharvest.read.summon</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustharvest.read.aura</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_rustharvest.read.field</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Poison;Blood</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_rustharvest</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z83" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>explode:1;linger:2;return:1</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>fw_cluster</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>fw_reclaim</t>
+        </is>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>limiter</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>fw_mix_steamshock</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>fusion.steamshock.name</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_steamshock.desc</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>2</v>
+      </c>
+      <c r="M84" t="n">
+        <v>2</v>
+      </c>
+      <c r="N84" t="n">
+        <v>7</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_steamshock.read.projectile</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_steamshock.read.melee</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_steamshock.read.summon</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_steamshock.read.aura</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>firmware.fw_mix_steamshock.read.field</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Wet;Fire</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>em</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>icon_fw_mix_steamshock</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>fusion</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>firmware.acquire.fusion</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Z84" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>grow:1;trail:2</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>fw_shockwave</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>fw_burntrail</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>fw_mix_floodarc</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>fusion.floodarc.name</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>reclaim</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>fluid</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
           <t>firmware.fw_mix_floodarc.desc</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>epic</t>
         </is>
       </c>
-      <c r="L77" t="n">
+      <c r="L85" t="n">
         <v>3</v>
       </c>
-      <c r="M77" t="n">
+      <c r="M85" t="n">
         <v>3</v>
       </c>
-      <c r="N77" t="n">
+      <c r="N85" t="n">
         <v>6</v>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>firmware.fw_mix_floodarc.read.projectile</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>firmware.fw_mix_floodarc.read.melee</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>firmware.fw_mix_floodarc.read.summon</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="R85" t="inlineStr">
         <is>
           <t>firmware.fw_mix_floodarc.read.aura</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>firmware.fw_mix_floodarc.read.field</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>Capillary;Wet;Shock</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="U85" t="inlineStr">
         <is>
           <t>fluid</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr">
+      <c r="V85" t="inlineStr">
         <is>
           <t>icon_fw_mix_floodarc</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr">
+      <c r="W85" t="inlineStr">
         <is>
           <t>fusion</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>firmware.acquire.fusion</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Y85" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="Z77" t="n">
+      <c r="Z85" t="n">
         <v>17</v>
       </c>
-      <c r="AA77" t="inlineStr">
+      <c r="AA85" t="inlineStr">
         <is>
           <t>linger:3;scale:1.2;chain:2</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
+      <c r="AB85" t="inlineStr">
         <is>
           <t>fw_spread</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
+      <c r="AC85" t="inlineStr">
         <is>
           <t>fw_arcchain</t>
         </is>
       </c>
-      <c r="AD77" t="inlineStr">
+      <c r="AD85" t="inlineStr">
         <is>
           <t>em</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
+++ b/Configs/GameConfig/Datas/fg/#FirmwareKind-固件种类.xlsx
@@ -3028,7 +3028,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>WallImpact</t>
+          <t>none</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
